--- a/Data/C04 Figures.xlsx
+++ b/Data/C04 Figures.xlsx
@@ -3222,10 +3222,10 @@
         <v>45658</v>
       </c>
       <c r="B258" t="n">
-        <v>18.6418765694586</v>
+        <v>18.6376775634266</v>
       </c>
       <c r="C258" t="n">
-        <v>5.61316618936084</v>
+        <v>5.62955151665529</v>
       </c>
     </row>
     <row r="259">
@@ -3233,10 +3233,10 @@
         <v>45748</v>
       </c>
       <c r="B259" t="n">
-        <v>18.8125451871058</v>
+        <v>18.8245611194087</v>
       </c>
       <c r="C259" t="n">
-        <v>5.66241180723492</v>
+        <v>5.69856536215979</v>
       </c>
     </row>
     <row r="260">
@@ -3244,10 +3244,21 @@
         <v>45839</v>
       </c>
       <c r="B260" t="n">
-        <v>18.5731276970108</v>
+        <v>18.5198136914227</v>
       </c>
       <c r="C260" t="n">
-        <v>5.50829131157048</v>
+        <v>5.49232385103167</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B261" t="n">
+        <v>18.4246292893727</v>
+      </c>
+      <c r="C261" t="n">
+        <v>5.38930411081911</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C04 Figures.xlsx
+++ b/Data/C04 Figures.xlsx
@@ -3222,10 +3222,10 @@
         <v>45658</v>
       </c>
       <c r="B258" t="n">
-        <v>18.6376775634266</v>
+        <v>18.6712036649949</v>
       </c>
       <c r="C258" t="n">
-        <v>5.62955151665529</v>
+        <v>5.63196474935896</v>
       </c>
     </row>
     <row r="259">
@@ -3233,10 +3233,10 @@
         <v>45748</v>
       </c>
       <c r="B259" t="n">
-        <v>18.8245611194087</v>
+        <v>18.8575201011441</v>
       </c>
       <c r="C259" t="n">
-        <v>5.69856536215979</v>
+        <v>5.71626090693373</v>
       </c>
     </row>
     <row r="260">
@@ -3244,10 +3244,10 @@
         <v>45839</v>
       </c>
       <c r="B260" t="n">
-        <v>18.5198136914227</v>
+        <v>18.5248974464661</v>
       </c>
       <c r="C260" t="n">
-        <v>5.49232385103167</v>
+        <v>5.48931284225402</v>
       </c>
     </row>
     <row r="261">
@@ -3255,10 +3255,21 @@
         <v>45931</v>
       </c>
       <c r="B261" t="n">
-        <v>18.4246292893727</v>
+        <v>18.3368345420115</v>
       </c>
       <c r="C261" t="n">
-        <v>5.38930411081911</v>
+        <v>5.32975296689379</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B262" t="n">
+        <v>18.0234273486055</v>
+      </c>
+      <c r="C262" t="n">
+        <v>5.10298086337017</v>
       </c>
     </row>
   </sheetData>
